--- a/tests/test_output/output.xlsx
+++ b/tests/test_output/output.xlsx
@@ -428,16 +428,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.1" customWidth="1" min="1" max="1"/>
     <col width="9.1" customWidth="1" min="2" max="2"/>
     <col width="11.7" customWidth="1" min="3" max="3"/>
-    <col width="15.6" customWidth="1" min="4" max="4"/>
+    <col width="9.1" customWidth="1" min="4" max="4"/>
     <col width="14.3" customWidth="1" min="5" max="5"/>
-    <col width="15.6" customWidth="1" min="6" max="6"/>
-    <col width="15.6" customWidth="1" min="7" max="7"/>
+    <col width="11.7" customWidth="1" min="6" max="6"/>
+    <col width="19.5" customWidth="1" min="7" max="7"/>
+    <col width="16.9" customWidth="1" min="8" max="8"/>
+    <col width="15.6" customWidth="1" min="9" max="9"/>
+    <col width="14.3" customWidth="1" min="10" max="10"/>
+    <col width="15.6" customWidth="1" min="11" max="11"/>
+    <col width="15.6" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="35" customHeight="1">
@@ -458,20 +463,45 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>ligand</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>solvent</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>concentration</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>temperature</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>pred yield</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>pred cost</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>yield</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>cost</t>
         </is>
@@ -491,20 +521,41 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>0.00±0.00</t>
+          <t>CsOAc</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>0.00±0.00</t>
+          <t>PPh3</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>[exp_data]</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+          <t>DMAc</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>0.00±0.00</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>0.00±0.00</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>[exp_data]</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>[exp_data]</t>
         </is>
@@ -524,20 +575,41 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>0.00±0.00</t>
+          <t>CsOAc</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>0.00±0.00</t>
+          <t>PPhtBu2</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>[exp_data]</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+          <t>DMAc</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>0.00±0.00</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>0.00±0.00</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>[exp_data]</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>[exp_data]</t>
         </is>
@@ -557,20 +629,41 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0.00±0.00</t>
+          <t>CsOAc</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0.00±0.00</t>
+          <t>PPh2Me</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>[exp_data]</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+          <t>DMAc</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0.00±0.00</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0.00±0.00</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>[exp_data]</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>[exp_data]</t>
         </is>
@@ -590,20 +683,41 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0.00±0.00</t>
+          <t>CsOAc</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0.00±0.00</t>
+          <t>CgMe-PPh</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>[exp_data]</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+          <t>DMAc</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0.00±0.00</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0.00±0.00</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>[exp_data]</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>[exp_data]</t>
         </is>
@@ -623,20 +737,41 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0.00±0.00</t>
+          <t>CsOAc</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0.00±0.00</t>
+          <t>BrettPhos</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>[exp_data]</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+          <t>DMAc</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0.00±0.00</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0.00±0.00</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>[exp_data]</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>[exp_data]</t>
         </is>
